--- a/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 8,46</t>
+          <t>-14,28; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 12,41</t>
+          <t>-8,14; 12,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 9,89</t>
+          <t>-31,8; 9,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 0,0</t>
+          <t>-35,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 5,23</t>
+          <t>-6,67; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,37</t>
+          <t>-4,31; 5,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,67</t>
+          <t>-3,59; 1,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,24</t>
+          <t>-5,31; 2,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 143,63</t>
+          <t>-67,69; 145,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 669,35</t>
+          <t>-74,67; 590,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,66</t>
+          <t>-100,0; 130,18</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 8,62</t>
+          <t>-13,12; 8,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 8,16</t>
+          <t>-8,23; 6,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -1,59</t>
+          <t>-24,22; -1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 634,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 3,13</t>
+          <t>-6,38; 2,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,16</t>
+          <t>-3,16; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,13</t>
+          <t>-7,35; 0,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,0</t>
+          <t>-4,75; 0,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 72,08</t>
+          <t>-66,78; 60,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 200,84</t>
+          <t>-57,44; 217,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 26,01</t>
+          <t>-93,38; 17,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 82,78</t>
+          <t>-89,86; 79,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 8,3</t>
+          <t>-14,22; 10,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 12,6</t>
+          <t>-9,16; 12,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 9,73</t>
+          <t>-37,68; 9,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 0,0</t>
+          <t>-38,22; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 4,64</t>
+          <t>-6,97; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 5,26</t>
+          <t>-4,42; 5,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,66</t>
+          <t>-4,13; 1,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,05</t>
+          <t>-5,08; 2,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 145,95</t>
+          <t>-74,0; 146,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 590,7</t>
+          <t>-80,2; 456,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 130,18</t>
+          <t>-100,0; 210,14</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 8,49</t>
+          <t>-13,34; 7,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 6,69</t>
+          <t>-8,42; 6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,22; -1,56</t>
+          <t>-23,71; -1,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 138,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 2,99</t>
+          <t>-6,45; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,18</t>
+          <t>-3,28; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,02</t>
+          <t>-7,17; -0,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,68</t>
+          <t>-4,67; 1,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 60,52</t>
+          <t>-63,75; 73,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 217,49</t>
+          <t>-56,74; 230,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-93,38; 17,24</t>
+          <t>-93,36; 29,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 79,94</t>
+          <t>-90,07; 104,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-12,63</t>
+          <t>-9,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 10,54</t>
+          <t>-14,24; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 12,2</t>
+          <t>-7,66; 12,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 9,33</t>
+          <t>-30,65; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 0,0</t>
+          <t>-31,41; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-33,2%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 5,3</t>
+          <t>-7,17; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,48</t>
+          <t>-3,97; 5,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,59</t>
+          <t>-3,88; 1,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,49</t>
+          <t>-5,15; 2,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 146,55</t>
+          <t>-67,69; 143,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,2; 456,86</t>
+          <t>-73,86; 669,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,14</t>
+          <t>-100,0; 247,86</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 7,67</t>
+          <t>-12,45; 8,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,93</t>
+          <t>-8,15; 8,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -1,72</t>
+          <t>-22,93; -1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 634,15</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 138,89</t>
+          <t>-100,0; 37,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-51,17%</t>
+          <t>-42,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 3,28</t>
+          <t>-6,58; 3,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,22</t>
+          <t>-3,38; 4,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -0,04</t>
+          <t>-7,58; -0,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,37</t>
+          <t>-4,62; 1,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 73,09</t>
+          <t>-62,55; 72,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 230,64</t>
+          <t>-59,61; 200,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-93,36; 29,08</t>
+          <t>-93,5; 26,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 104,97</t>
+          <t>-88,42; 133,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,179 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-14,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-51,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1760820653687746</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7919303473075691</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.01067310506860167</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.271300379939135</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1139056482334251</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.116590509388737</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.008215548859528004</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-14,24; 8,46</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,66; 12,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-30,65; 9,89</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-31,41; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.239919384232009</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.356517148089688</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.925506747303388</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.151252893164038</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.102205330891781</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.36264671583638</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.631194555545876</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,87%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-33,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-33,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 5,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 5,37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,88; 1,67</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 2,85</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-67,69; 143,63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-73,86; 669,35</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 247,86</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1465629373136495</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1192792159706225</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.09588819919089725</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3009774526161024</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1120904289207729</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1685347366636631</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3323851389066212</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3685082241462916</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,86</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-11,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-34,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-20,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-81,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.23540645379141</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.8558300468436314</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7398623722215829</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.266308222735895</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6761081987849761</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.795778492214028</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,45; 8,62</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,15; 8,16</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-22,93; -1,59</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 634,15</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 37,9</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.102455131682567</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.011088576162337</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2899058262060368</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.5339440491707297</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.136486572425751</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.514892132210103</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>1.5977899384468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +799,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-62,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-42,14%</t>
+      <c r="C10" s="5" t="n">
+        <v>-1.135236869310368</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.2835701161573123</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.676075665114827</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.2443155704909882</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.6222054797380743</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2466105654505386</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.8040464105148317</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,52 +830,152 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,58; 3,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,16</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,58; -0,13</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 1,44</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-62,55; 72,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-59,61; 200,84</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-93,5; 26,01</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-88,42; 133,1</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.400730876875555</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.926572624607801</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.046594330393768</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5816414181886777</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.463466632089069</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.1577728796276509</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.268638446538008</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3811699924689056</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1149183641549036</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.4957886021182859</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.3249839470816051</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.262975766430129</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1421453511651179</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5946864788720646</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4402691319027056</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.331987723131308</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.6716364046495815</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.132153178435306</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.046871445012634</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6781996122527792</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6180973785943971</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.9107462189744483</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8884168128641911</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5762871862663942</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8646352816006835</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1955701114335468</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.3026000821599145</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6258271887538052</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.044238349525745</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.047053348585441</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.009441433596883</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +983,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
